--- a/output/pdf_financials_xlsx/WRN.xlsx
+++ b/output/pdf_financials_xlsx/WRN.xlsx
@@ -1303,58 +1303,58 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.225966</v>
+        <v>-3.225966</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>5.297251</v>
+        <v>-2.776979</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>20.060677</v>
+        <v>-23.950949</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.913276</v>
+        <v>-3.913276</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.118027</v>
+        <v>-2.118027</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>2.0884</v>
+        <v>-2.0884</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.85616</v>
+        <v>-2.85616</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.766448</v>
+        <v>-1.766448</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>3.708887</v>
+        <v>-3.708887</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>4.994178</v>
+        <v>-4.994178</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>3.338299</v>
+        <v>-3.338299</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>6.92183</v>
+        <v>-6.92183</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>3.119762</v>
+        <v>-3.119762</v>
       </c>
     </row>
     <row r="17">
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.225966</v>
+        <v>-3.225966</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.037115</v>
+        <v>-4.037115</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>22.005813</v>
+        <v>-22.005813</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>3.913276</v>
+        <v>-3.913276</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.118027</v>
+        <v>-2.118027</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.0884</v>
+        <v>-2.0884</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.85616</v>
+        <v>-2.85616</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.766448</v>
+        <v>-1.766448</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>3.708887</v>
+        <v>-3.708887</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>4.994178</v>
+        <v>-4.994178</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>3.338299</v>
+        <v>-3.338299</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>6.92183</v>
+        <v>-6.92183</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>3.119762</v>
+        <v>-3.119762</v>
       </c>
     </row>
     <row r="21">
@@ -1802,58 +1802,58 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.225966</v>
+        <v>-3.225966</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.037115</v>
+        <v>-4.037115</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>22.005813</v>
+        <v>-22.005813</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3.913276</v>
+        <v>-3.913276</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.118027</v>
+        <v>-2.118027</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2.0884</v>
+        <v>-2.0884</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.85616</v>
+        <v>-2.85616</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.766448</v>
+        <v>-1.766448</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>3.708887</v>
+        <v>-3.708887</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>4.994178</v>
+        <v>-4.994178</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>3.338299</v>
+        <v>-3.338299</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>6.92183</v>
+        <v>-6.92183</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3.119762</v>
+        <v>-3.119762</v>
       </c>
     </row>
     <row r="24">
@@ -1985,22 +1985,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>64.51931999999999</v>
+        <v>-64.51931999999999</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>71.97496700000001</v>
+        <v>-71.97496700000001</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>93.00785</v>
+        <v>-93.00785</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>80.7423</v>
+        <v>-80.7423</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>91.690888</v>
+        <v>-91.690888</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>97.8319</v>
+        <v>-97.8319</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -2008,37 +2008,37 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>95.59869999999999</v>
+        <v>-95.59869999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>105.90135</v>
+        <v>-105.90135</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>104.42</v>
+        <v>-104.42</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>88.719633</v>
+        <v>-88.719633</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>95.205333</v>
+        <v>-95.205333</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>88.3224</v>
+        <v>-88.3224</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>123.629567</v>
+        <v>-123.629567</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>166.4726</v>
+        <v>-166.4726</v>
       </c>
       <c r="Q26" s="3" t="n">
-        <v>166.91495</v>
+        <v>-166.91495</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>173.04575</v>
+        <v>-173.04575</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>155.9881</v>
+        <v>-155.9881</v>
       </c>
     </row>
     <row r="27">
@@ -2048,58 +2048,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.225966</v>
+        <v>-3.225966</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5.297251</v>
+        <v>-2.776979</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>20.060677</v>
+        <v>-23.950949</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.913276</v>
+        <v>-3.913276</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.118027</v>
+        <v>-2.118027</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>2.0884</v>
+        <v>-2.0884</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.85616</v>
+        <v>-2.85616</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.766448</v>
+        <v>-1.766448</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>3.708887</v>
+        <v>-3.708887</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>4.994178</v>
+        <v>-4.994178</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>3.338299</v>
+        <v>-3.338299</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>6.92183</v>
+        <v>-6.92183</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>3.119762</v>
+        <v>-3.119762</v>
       </c>
     </row>
     <row r="28">
@@ -2170,58 +2170,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.225966</v>
+        <v>-3.225966</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.297251</v>
+        <v>-2.776979</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>20.060677</v>
+        <v>-23.950949</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.913276</v>
+        <v>-3.913276</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.118027</v>
+        <v>-2.118027</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.0884</v>
+        <v>-2.0884</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.85616</v>
+        <v>-2.85616</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.766448</v>
+        <v>-1.766448</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>3.812148</v>
+        <v>-3.605626</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>5.162072</v>
+        <v>-4.826284</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>3.545199</v>
+        <v>-3.131399</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>7.079489</v>
+        <v>-6.764171</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>3.217323</v>
+        <v>-3.022201</v>
       </c>
     </row>
     <row r="30">
@@ -2328,58 +2328,58 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>23.78848953919684</v>
+        <v>-45.37794488183022</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>9.696262992520142</v>
+        <v>-8.121331643268082</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -8139,10 +8139,10 @@
         <v>0</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-13.824762</v>
       </c>
       <c r="S118" s="3" t="n">
-        <v>0</v>
+        <v>-20.506602</v>
       </c>
     </row>
     <row r="119">
@@ -29032,7 +29032,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -57114,28 +57118,28 @@
         </is>
       </c>
       <c r="O457" s="5" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="P457" s="5" t="n">
-        <v>2.85616</v>
+        <v>-2.85616</v>
       </c>
       <c r="Q457" s="5" t="n">
-        <v>1.766448</v>
+        <v>-1.766448</v>
       </c>
       <c r="R457" s="5" t="n">
-        <v>3.708887</v>
+        <v>-3.708887</v>
       </c>
       <c r="S457" s="5" t="n">
-        <v>4.994178</v>
+        <v>-4.994178</v>
       </c>
       <c r="T457" s="5" t="n">
-        <v>3.338299</v>
+        <v>-3.338299</v>
       </c>
       <c r="U457" s="5" t="n">
-        <v>6.92183</v>
+        <v>-6.92183</v>
       </c>
       <c r="V457" s="5" t="n">
-        <v>3.119762</v>
+        <v>-3.119762</v>
       </c>
     </row>
     <row r="458">
@@ -59700,19 +59704,19 @@
         </is>
       </c>
       <c r="K483" s="5" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="L483" s="5" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="M483" s="5" t="n">
-        <v>2.118027</v>
+        <v>-2.118027</v>
       </c>
       <c r="N483" s="5" t="n">
-        <v>2.0884</v>
+        <v>-2.0884</v>
       </c>
       <c r="O483" s="5" t="n">
-        <v>2.661589</v>
+        <v>-2.661589</v>
       </c>
       <c r="P483" t="inlineStr">
         <is>
@@ -60978,28 +60982,28 @@
         </is>
       </c>
       <c r="E496" s="5" t="n">
-        <v>3.225966</v>
+        <v>-3.225966</v>
       </c>
       <c r="F496" s="5" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="G496" s="5" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="H496" s="5" t="n">
-        <v>4.037115</v>
+        <v>-4.037115</v>
       </c>
       <c r="I496" s="5" t="n">
-        <v>22.005813</v>
+        <v>-22.005813</v>
       </c>
       <c r="J496" s="5" t="n">
-        <v>3.913276</v>
+        <v>-3.913276</v>
       </c>
       <c r="K496" s="5" t="n">
-        <v>1.365516</v>
+        <v>-1.365516</v>
       </c>
       <c r="L496" s="5" t="n">
-        <v>1.911974</v>
+        <v>-1.911974</v>
       </c>
       <c r="M496" t="inlineStr">
         <is>
@@ -65721,13 +65725,13 @@
         </is>
       </c>
       <c r="F541" s="5" t="n">
-        <v>2.159249</v>
+        <v>-2.159249</v>
       </c>
       <c r="G541" s="5" t="n">
-        <v>1.860157</v>
+        <v>-1.860157</v>
       </c>
       <c r="H541" s="5" t="n">
-        <v>2.776979</v>
+        <v>-2.776979</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WRN.xlsx
+++ b/output/pdf_financials_xlsx/WRN.xlsx
@@ -1059,58 +1059,58 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-1.276014</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.599575</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.238166</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057686</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.245054</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.07283000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.238873</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.23629</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.163771</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.095207</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046728</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.08358400000000001</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057866</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.20796</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.584512</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-1.17695</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-2.676508</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-1.968352</v>
       </c>
     </row>
     <row r="13">
@@ -2048,58 +2048,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.225966</v>
+        <v>-1.949952</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.159249</v>
+        <v>-1.559674</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.860157</v>
+        <v>-1.621991</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.776979</v>
+        <v>-2.719293</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-23.950949</v>
+        <v>-23.705895</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.913276</v>
+        <v>-3.840446</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.365516</v>
+        <v>-1.126643</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.911974</v>
+        <v>-1.675684</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.118027</v>
+        <v>-1.954256</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.0884</v>
+        <v>-1.993193</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.661589</v>
+        <v>-2.614861</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.85616</v>
+        <v>-2.772576</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-1.766448</v>
+        <v>-1.708582</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.708887</v>
+        <v>-3.500927</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-4.994178</v>
+        <v>-4.409666</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-3.338299</v>
+        <v>-2.161349</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-6.92183</v>
+        <v>-4.245322</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-3.119762</v>
+        <v>-1.15141</v>
       </c>
     </row>
     <row r="28">
@@ -2170,58 +2170,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.225966</v>
+        <v>-1.949952</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.159249</v>
+        <v>-1.559674</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.860157</v>
+        <v>-1.621991</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.776979</v>
+        <v>-2.719293</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-23.950949</v>
+        <v>-23.705895</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.913276</v>
+        <v>-3.840446</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.365516</v>
+        <v>-1.126643</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.911974</v>
+        <v>-1.675684</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.118027</v>
+        <v>-1.954256</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.0884</v>
+        <v>-1.993193</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.661589</v>
+        <v>-2.614861</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.85616</v>
+        <v>-2.772576</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.766448</v>
+        <v>-1.708582</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.605626</v>
+        <v>-3.397666</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-4.826284</v>
+        <v>-4.241772</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-3.131399</v>
+        <v>-1.954449</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-6.764171</v>
+        <v>-4.087663</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-3.022201</v>
+        <v>-1.053849</v>
       </c>
     </row>
     <row r="30">
@@ -8542,19 +8542,19 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.10861</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.209062</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.245672</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.188174</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.109696</v>
       </c>
     </row>
     <row r="125">
@@ -8605,19 +8605,19 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.10861</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.209062</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.245672</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.188174</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.109696</v>
       </c>
     </row>
     <row r="126">
@@ -28766,7 +28766,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -56866,7 +56870,7 @@
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -59472,7 +59476,7 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -60880,7 +60884,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E495" s="5" t="n">
@@ -64460,7 +64464,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">

--- a/output/pdf_financials_xlsx/WRN.xlsx
+++ b/output/pdf_financials_xlsx/WRN.xlsx
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3.225966</v>
+        <v>-4.747245</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.159249</v>
+        <v>-2.610952</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.860157</v>
+        <v>-2.256054</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-2.776979</v>
@@ -1364,13 +1364,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>1.521279</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.451703</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.395897</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-1.260136</v>
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.949952</v>
+        <v>-3.471231</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.559674</v>
+        <v>-2.011377</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.621991</v>
+        <v>-2.017888</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.719293</v>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.949952</v>
+        <v>-3.471231</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.559674</v>
+        <v>-2.011377</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.621991</v>
+        <v>-2.017888</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.719293</v>
@@ -2328,13 +2328,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-32.04551271316311</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-17.30031804491236</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-17.54820584968268</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-45.37794488183022</v>
@@ -4972,19 +4972,19 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.171167</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.245673</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.185515</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.033408</v>
       </c>
       <c r="S70" s="3" t="n">
-        <v>0</v>
+        <v>0.033408</v>
       </c>
     </row>
     <row r="71">
@@ -5037,19 +5037,19 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.171167</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.245673</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.185515</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.033408</v>
       </c>
       <c r="S71" s="3" t="n">
-        <v>0</v>
+        <v>0.033408</v>
       </c>
     </row>
     <row r="72">
@@ -5297,19 +5297,19 @@
         <v>0.08977499999999999</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.930692</v>
+        <v>0.759525</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.245673</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.185515</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.033408</v>
+        <v>0</v>
       </c>
       <c r="S75" s="3" t="n">
-        <v>0.033408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5653,25 +5653,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>0.001527371681620454</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.002238637094067116</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.001330388309306407</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.0001761930045850053</v>
       </c>
       <c r="S80" s="1" t="inlineStr">
         <is>
@@ -7953,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>3.453554</v>
       </c>
     </row>
     <row r="116">
@@ -11042,7 +11034,11 @@
           <t>Current portion of lease obligation 172,110</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -13166,7 +13162,11 @@
           <t>Current portion of lease obligation</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -29144,7 +29144,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -31872,7 +31876,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -48198,7 +48206,11 @@
           <t>Future income tax recovery 14</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -52732,7 +52744,11 @@
           <t>Future income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E415" s="5" t="n">
         <v>-1.521279</v>
       </c>
@@ -65614,7 +65630,11 @@
           <t>FUTURE INCOME TAX RECOVERY 14</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -66766,7 +66786,11 @@
           <t>FUTURE INCOME TAX RECOVERY (note 14)</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E551" s="5" t="n">
         <v>-1.521279</v>
       </c>
